--- a/results/02_taxa_assemblage/WardsClustering/tables/pvclust_AU_sweep_2_(40, 70).xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/pvclust_AU_sweep_2_(40, 70).xlsx
@@ -481,22 +481,22 @@
         <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9044</v>
+        <v>0.8799</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0044</v>
+        <v>0.0487</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9522</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0139</v>
+        <v>0.0459</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -510,22 +510,22 @@
         <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5891</v>
+        <v>0.7867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1244</v>
+        <v>0.0181</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6149</v>
+        <v>0.7484</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1502</v>
+        <v>0.0173</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -539,22 +539,22 @@
         <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6217</v>
+        <v>0.8552</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1229</v>
+        <v>0.019</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6331</v>
+        <v>0.8274</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1479</v>
+        <v>0.0183</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -568,22 +568,22 @@
         <v>43</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5833</v>
+        <v>0.7733</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0163</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5709</v>
+        <v>0.7316</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1045</v>
+        <v>0.0162</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -597,22 +597,22 @@
         <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5931</v>
+        <v>0.8066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5703</v>
+        <v>0.8066</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1108</v>
+        <v>0.0263</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -626,22 +626,22 @@
         <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5979</v>
+        <v>0.7873</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0898</v>
+        <v>0.0203</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5769</v>
+        <v>0.7587</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1107</v>
+        <v>0.0194</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -655,22 +655,22 @@
         <v>46</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5068</v>
+        <v>0.802</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0326</v>
+        <v>0.0197</v>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5615</v>
+        <v>0.7796</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0397</v>
+        <v>0.0193</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -684,22 +684,22 @@
         <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5669</v>
+        <v>0.7887</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0322</v>
+        <v>0.0182</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5961</v>
+        <v>0.7603</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0379</v>
+        <v>0.0178</v>
       </c>
       <c r="I9" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -713,22 +713,22 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5581</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0431</v>
+        <v>0.0145</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.4383</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0491</v>
+        <v>0.0137</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -742,22 +742,22 @@
         <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5525</v>
+        <v>0.423</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0428</v>
+        <v>0.0138</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.623</v>
+        <v>0.358</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0488</v>
+        <v>0.0132</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -771,22 +771,22 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5893</v>
+        <v>0.6682</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0421</v>
+        <v>0.0157</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6595</v>
+        <v>0.6299</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0495</v>
+        <v>0.0151</v>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -800,19 +800,19 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>0.064</v>
+        <v>0.6041</v>
       </c>
       <c r="E13" t="n">
-        <v>0.064</v>
+        <v>0.0181</v>
       </c>
       <c r="F13" t="n">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.046</v>
+        <v>0.6146</v>
       </c>
       <c r="H13" t="n">
-        <v>0.046</v>
+        <v>0.0182</v>
       </c>
       <c r="I13" t="n">
         <v>35</v>
@@ -829,19 +829,19 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>0.064</v>
+        <v>0.4697</v>
       </c>
       <c r="E14" t="n">
-        <v>0.064</v>
+        <v>0.0178</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.076</v>
+        <v>0.4336</v>
       </c>
       <c r="H14" t="n">
-        <v>0.076</v>
+        <v>0.0163</v>
       </c>
       <c r="I14" t="n">
         <v>35</v>
@@ -858,22 +858,22 @@
         <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>0.124</v>
+        <v>0.6737</v>
       </c>
       <c r="E15" t="n">
-        <v>0.124</v>
+        <v>0.0166</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2906</v>
+        <v>0.6515</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0045</v>
+        <v>0.0156</v>
       </c>
       <c r="I15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -887,22 +887,22 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>0.098</v>
+        <v>0.6926</v>
       </c>
       <c r="E16" t="n">
-        <v>0.098</v>
+        <v>0.0174</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2906</v>
+        <v>0.6701</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0045</v>
+        <v>0.0164</v>
       </c>
       <c r="I16" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -916,22 +916,22 @@
         <v>55</v>
       </c>
       <c r="D17" t="n">
-        <v>0.066</v>
+        <v>0.6498</v>
       </c>
       <c r="E17" t="n">
-        <v>0.066</v>
+        <v>0.0171</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.052</v>
+        <v>0.6519</v>
       </c>
       <c r="H17" t="n">
-        <v>0.052</v>
+        <v>0.0154</v>
       </c>
       <c r="I17" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -945,22 +945,22 @@
         <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05</v>
+        <v>0.6126</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05</v>
+        <v>0.0153</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>0.062</v>
+        <v>0.6089</v>
       </c>
       <c r="H18" t="n">
-        <v>0.062</v>
+        <v>0.0149</v>
       </c>
       <c r="I18" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -974,22 +974,22 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.673</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0175</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.6771</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="I19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -1003,22 +1003,22 @@
         <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1289</v>
+        <v>0.5769</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0039</v>
+        <v>0.0131</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1289</v>
+        <v>0.544</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0039</v>
+        <v>0.0132</v>
       </c>
       <c r="I20" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -1032,22 +1032,22 @@
         <v>59</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7663</v>
+        <v>0.5567</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0044</v>
+        <v>0.0151</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8563</v>
+        <v>0.5271</v>
       </c>
       <c r="H21" t="n">
-        <v>0.005</v>
+        <v>0.0146</v>
       </c>
       <c r="I21" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
@@ -1061,22 +1061,22 @@
         <v>60</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4868</v>
+        <v>0.8403</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0035</v>
+        <v>0.0345</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4868</v>
+        <v>0.8461</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0035</v>
+        <v>0.0324</v>
       </c>
       <c r="I22" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -1090,22 +1090,22 @@
         <v>61</v>
       </c>
       <c r="D23" t="n">
-        <v>0.054</v>
+        <v>0.907</v>
       </c>
       <c r="E23" t="n">
-        <v>0.054</v>
+        <v>0.0361</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>0.056</v>
+        <v>0.9134</v>
       </c>
       <c r="H23" t="n">
-        <v>0.056</v>
+        <v>0.0339</v>
       </c>
       <c r="I23" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
@@ -1119,22 +1119,22 @@
         <v>62</v>
       </c>
       <c r="D24" t="n">
-        <v>0.058</v>
+        <v>0.6708</v>
       </c>
       <c r="E24" t="n">
-        <v>0.058</v>
+        <v>0.0199</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.066</v>
+        <v>0.6708</v>
       </c>
       <c r="H24" t="n">
-        <v>0.066</v>
+        <v>0.0199</v>
       </c>
       <c r="I24" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -1148,22 +1148,22 @@
         <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4899</v>
+        <v>0.7714</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0035</v>
+        <v>0.0208</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4899</v>
+        <v>0.7714</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0035</v>
+        <v>0.0208</v>
       </c>
       <c r="I25" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
@@ -1177,22 +1177,22 @@
         <v>64</v>
       </c>
       <c r="D26" t="n">
-        <v>0.481</v>
+        <v>0.8008</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0034</v>
+        <v>0.0192</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.481</v>
+        <v>0.8008</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0034</v>
+        <v>0.0192</v>
       </c>
       <c r="I26" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -1206,22 +1206,22 @@
         <v>65</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5258</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0034</v>
+        <v>0.0236</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5258</v>
+        <v>0.8853</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0034</v>
+        <v>0.0232</v>
       </c>
       <c r="I27" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28">
@@ -1235,22 +1235,22 @@
         <v>66</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5228</v>
+        <v>0.8721</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0034</v>
+        <v>0.0252</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5228</v>
+        <v>0.8687</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0034</v>
+        <v>0.0245</v>
       </c>
       <c r="I28" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
@@ -1264,22 +1264,22 @@
         <v>67</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5228</v>
+        <v>0.9283</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0034</v>
+        <v>0.0225</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5228</v>
+        <v>0.9285</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0034</v>
+        <v>0.0213</v>
       </c>
       <c r="I29" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>0.028</v>
+        <v>0.9267</v>
       </c>
       <c r="E30" t="n">
-        <v>0.028</v>
+        <v>0.0209</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.026</v>
+        <v>0.9314</v>
       </c>
       <c r="H30" t="n">
-        <v>0.026</v>
+        <v>0.0202</v>
       </c>
       <c r="I30" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
@@ -1322,22 +1322,22 @@
         <v>69</v>
       </c>
       <c r="D31" t="n">
-        <v>0.032</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03</v>
+        <v>0.8972</v>
       </c>
       <c r="H31" t="n">
-        <v>0.03</v>
+        <v>0.0175</v>
       </c>
       <c r="I31" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
@@ -1351,22 +1351,22 @@
         <v>70</v>
       </c>
       <c r="D32" t="n">
-        <v>0.024</v>
+        <v>0.6359</v>
       </c>
       <c r="E32" t="n">
-        <v>0.024</v>
+        <v>0.0213</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>0.036</v>
+        <v>0.6359</v>
       </c>
       <c r="H32" t="n">
-        <v>0.036</v>
+        <v>0.0213</v>
       </c>
       <c r="I32" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
